--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_11-03-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_11-03-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="371">
   <si>
     <t>SKU</t>
   </si>
@@ -511,12 +511,75 @@
     <t>£1276.0</t>
   </si>
   <si>
-    <t>£0.0</t>
+    <t>£29.33</t>
+  </si>
+  <si>
+    <t>£85.79</t>
+  </si>
+  <si>
+    <t>£35.08</t>
+  </si>
+  <si>
+    <t>£13.65</t>
+  </si>
+  <si>
+    <t>£14.29</t>
+  </si>
+  <si>
+    <t>£24.65</t>
   </si>
   <si>
     <t>POA</t>
   </si>
   <si>
+    <t>£16.75</t>
+  </si>
+  <si>
+    <t>£26.79</t>
+  </si>
+  <si>
+    <t>£20.54</t>
+  </si>
+  <si>
+    <t>£47.29</t>
+  </si>
+  <si>
+    <t>£49.49</t>
+  </si>
+  <si>
+    <t>£567.48</t>
+  </si>
+  <si>
+    <t>£422.4</t>
+  </si>
+  <si>
+    <t>£41.93</t>
+  </si>
+  <si>
+    <t>£74.4</t>
+  </si>
+  <si>
+    <t>£170.21</t>
+  </si>
+  <si>
+    <t>£27.29</t>
+  </si>
+  <si>
+    <t>£686.32</t>
+  </si>
+  <si>
+    <t>£42.84</t>
+  </si>
+  <si>
+    <t>£1608.0</t>
+  </si>
+  <si>
+    <t>£1716.8</t>
+  </si>
+  <si>
+    <t>£1504.0</t>
+  </si>
+  <si>
     <t>£13.29</t>
   </si>
   <si>
@@ -754,15 +817,12 @@
     <t>£1984.64</t>
   </si>
   <si>
-    <t>£23.87</t>
-  </si>
-  <si>
-    <t>£27.67</t>
-  </si>
-  <si>
     <t>£29.74</t>
   </si>
   <si>
+    <t>£32.42</t>
+  </si>
+  <si>
     <t>£39.12</t>
   </si>
   <si>
@@ -784,6 +844,9 @@
     <t>£74.18</t>
   </si>
   <si>
+    <t>£81.55</t>
+  </si>
+  <si>
     <t>£86.21</t>
   </si>
   <si>
@@ -793,9 +856,6 @@
     <t>£51.20</t>
   </si>
   <si>
-    <t>£59.20</t>
-  </si>
-  <si>
     <t>£79.58</t>
   </si>
   <si>
@@ -892,9 +952,6 @@
     <t>£26.8</t>
   </si>
   <si>
-    <t>£32.42</t>
-  </si>
-  <si>
     <t>£32.98</t>
   </si>
   <si>
@@ -1025,9 +1082,6 @@
   </si>
   <si>
     <t>£29.78</t>
-  </si>
-  <si>
-    <t>£29.33</t>
   </si>
   <si>
     <t>£36.01</t>
@@ -1518,31 +1572,31 @@
         <v>165</v>
       </c>
       <c r="J2" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="K2" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="L2" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="M2" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="N2" t="s">
-        <v>246</v>
+        <v>171</v>
       </c>
       <c r="O2" t="s">
         <v>74</v>
       </c>
       <c r="P2" t="s">
-        <v>286</v>
+        <v>306</v>
       </c>
       <c r="Q2" t="s">
-        <v>306</v>
+        <v>325</v>
       </c>
       <c r="R2" t="s">
-        <v>329</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1574,31 +1628,31 @@
         <v>166</v>
       </c>
       <c r="J3" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="K3" t="s">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="L3" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="M3" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="N3" t="s">
-        <v>247</v>
+        <v>171</v>
       </c>
       <c r="O3" t="s">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="P3" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="Q3" t="s">
-        <v>307</v>
+        <v>326</v>
       </c>
       <c r="R3" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1627,34 +1681,34 @@
         <v>142</v>
       </c>
       <c r="I4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="J4" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="K4" t="s">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="L4" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="M4" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="N4" t="s">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="O4" t="s">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="P4" t="s">
         <v>76</v>
       </c>
       <c r="Q4" t="s">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="R4" t="s">
-        <v>330</v>
+        <v>349</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1683,34 +1737,34 @@
         <v>143</v>
       </c>
       <c r="I5" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="J5" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="K5" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="L5" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="M5" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="N5" t="s">
-        <v>166</v>
+        <v>268</v>
       </c>
       <c r="O5" t="s">
         <v>77</v>
       </c>
       <c r="P5" t="s">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="Q5" t="s">
-        <v>309</v>
+        <v>328</v>
       </c>
       <c r="R5" t="s">
-        <v>331</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1739,34 +1793,34 @@
         <v>144</v>
       </c>
       <c r="I6" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="J6" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="K6" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
       <c r="L6" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="M6" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="N6" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="O6" t="s">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="P6" t="s">
         <v>78</v>
       </c>
       <c r="Q6" t="s">
-        <v>310</v>
+        <v>329</v>
       </c>
       <c r="R6" t="s">
-        <v>332</v>
+        <v>351</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1795,34 +1849,34 @@
         <v>145</v>
       </c>
       <c r="I7" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="J7" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="K7" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="L7" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="M7" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="N7" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="O7" t="s">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="P7" t="s">
-        <v>289</v>
+        <v>309</v>
       </c>
       <c r="Q7" t="s">
         <v>79</v>
       </c>
       <c r="R7" t="s">
-        <v>333</v>
+        <v>352</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1851,34 +1905,34 @@
         <v>145</v>
       </c>
       <c r="I8" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="J8" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="K8" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="L8" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="M8" t="s">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="N8" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="O8" t="s">
-        <v>266</v>
+        <v>286</v>
       </c>
       <c r="P8" t="s">
-        <v>289</v>
+        <v>309</v>
       </c>
       <c r="Q8" t="s">
-        <v>311</v>
+        <v>330</v>
       </c>
       <c r="R8" t="s">
-        <v>334</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1907,34 +1961,34 @@
         <v>146</v>
       </c>
       <c r="I9" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="J9" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="K9" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="L9" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="M9" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="N9" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="O9" t="s">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="P9" t="s">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="Q9" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="R9" t="s">
-        <v>335</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1963,34 +2017,34 @@
         <v>147</v>
       </c>
       <c r="I10" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="J10" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="K10" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="L10" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="M10" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="N10" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="O10" t="s">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="P10" t="s">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="Q10" t="s">
-        <v>313</v>
+        <v>332</v>
       </c>
       <c r="R10" t="s">
-        <v>336</v>
+        <v>355</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -2019,34 +2073,34 @@
         <v>148</v>
       </c>
       <c r="I11" t="s">
+        <v>173</v>
+      </c>
+      <c r="J11" t="s">
+        <v>197</v>
+      </c>
+      <c r="K11" t="s">
+        <v>220</v>
+      </c>
+      <c r="L11" t="s">
+        <v>238</v>
+      </c>
+      <c r="M11" t="s">
+        <v>248</v>
+      </c>
+      <c r="N11" t="s">
+        <v>274</v>
+      </c>
+      <c r="O11" t="s">
+        <v>289</v>
+      </c>
+      <c r="P11" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>333</v>
+      </c>
+      <c r="R11" t="s">
         <v>165</v>
-      </c>
-      <c r="J11" t="s">
-        <v>176</v>
-      </c>
-      <c r="K11" t="s">
-        <v>199</v>
-      </c>
-      <c r="L11" t="s">
-        <v>217</v>
-      </c>
-      <c r="M11" t="s">
-        <v>227</v>
-      </c>
-      <c r="N11" t="s">
-        <v>254</v>
-      </c>
-      <c r="O11" t="s">
-        <v>269</v>
-      </c>
-      <c r="P11" t="s">
-        <v>291</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>314</v>
-      </c>
-      <c r="R11" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -2075,34 +2129,34 @@
         <v>101</v>
       </c>
       <c r="I12" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="J12" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="K12" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="L12" t="s">
         <v>101</v>
       </c>
       <c r="M12" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="N12" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="O12" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="P12" t="s">
-        <v>292</v>
+        <v>268</v>
       </c>
       <c r="Q12" t="s">
-        <v>292</v>
+        <v>268</v>
       </c>
       <c r="R12" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2131,34 +2185,34 @@
         <v>149</v>
       </c>
       <c r="I13" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="J13" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="K13" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="L13" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="M13" t="s">
-        <v>229</v>
+        <v>250</v>
       </c>
       <c r="N13" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="O13" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="P13" t="s">
-        <v>293</v>
+        <v>312</v>
       </c>
       <c r="Q13" t="s">
         <v>84</v>
       </c>
       <c r="R13" t="s">
-        <v>339</v>
+        <v>357</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2187,34 +2241,34 @@
         <v>150</v>
       </c>
       <c r="I14" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="J14" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="K14" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="L14" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="M14" t="s">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="N14" t="s">
-        <v>166</v>
+        <v>276</v>
       </c>
       <c r="O14" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="P14" t="s">
-        <v>294</v>
+        <v>313</v>
       </c>
       <c r="Q14" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="R14" t="s">
-        <v>340</v>
+        <v>358</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2243,31 +2297,31 @@
         <v>151</v>
       </c>
       <c r="I15" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="J15" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="K15" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="L15" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="M15" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="N15" t="s">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="O15" t="s">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="P15" t="s">
         <v>86</v>
       </c>
       <c r="Q15" t="s">
-        <v>316</v>
+        <v>335</v>
       </c>
       <c r="R15" t="s">
         <v>101</v>
@@ -2299,22 +2353,22 @@
         <v>152</v>
       </c>
       <c r="I16" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="J16" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="K16" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="L16" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="M16" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="N16" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="O16" t="s">
         <v>87</v>
@@ -2323,10 +2377,10 @@
         <v>87</v>
       </c>
       <c r="Q16" t="s">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="R16" t="s">
-        <v>341</v>
+        <v>359</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2355,31 +2409,31 @@
         <v>153</v>
       </c>
       <c r="I17" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="J17" t="s">
         <v>101</v>
       </c>
       <c r="K17" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="L17" t="s">
         <v>101</v>
       </c>
       <c r="M17" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="N17" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="O17" t="s">
-        <v>274</v>
+        <v>294</v>
       </c>
       <c r="P17" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
       <c r="Q17" t="s">
-        <v>318</v>
+        <v>337</v>
       </c>
       <c r="R17" t="s">
         <v>101</v>
@@ -2411,34 +2465,34 @@
         <v>154</v>
       </c>
       <c r="I18" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="J18" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="K18" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="L18" t="s">
         <v>101</v>
       </c>
       <c r="M18" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="N18" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="O18" t="s">
-        <v>275</v>
+        <v>295</v>
       </c>
       <c r="P18" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
       <c r="Q18" t="s">
-        <v>319</v>
+        <v>338</v>
       </c>
       <c r="R18" t="s">
-        <v>342</v>
+        <v>360</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2467,34 +2521,34 @@
         <v>155</v>
       </c>
       <c r="I19" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="J19" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="K19" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="L19" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="M19" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="N19" t="s">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="O19" t="s">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="P19" t="s">
-        <v>297</v>
+        <v>316</v>
       </c>
       <c r="Q19" t="s">
-        <v>320</v>
+        <v>339</v>
       </c>
       <c r="R19" t="s">
-        <v>343</v>
+        <v>361</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2523,34 +2577,34 @@
         <v>156</v>
       </c>
       <c r="I20" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="J20" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="K20" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="L20" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="M20" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="N20" t="s">
-        <v>259</v>
+        <v>171</v>
       </c>
       <c r="O20" t="s">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="P20" t="s">
         <v>91</v>
       </c>
       <c r="Q20" t="s">
-        <v>321</v>
+        <v>340</v>
       </c>
       <c r="R20" t="s">
-        <v>344</v>
+        <v>362</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2579,34 +2633,34 @@
         <v>157</v>
       </c>
       <c r="I21" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="J21" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="K21" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="L21" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="M21" t="s">
-        <v>237</v>
+        <v>258</v>
       </c>
       <c r="N21" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="O21" t="s">
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>298</v>
+        <v>317</v>
       </c>
       <c r="Q21" t="s">
-        <v>322</v>
+        <v>341</v>
       </c>
       <c r="R21" t="s">
-        <v>345</v>
+        <v>363</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2635,34 +2689,34 @@
         <v>158</v>
       </c>
       <c r="I22" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="J22" t="s">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="K22" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="L22" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="M22" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="N22" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="O22" t="s">
-        <v>278</v>
+        <v>298</v>
       </c>
       <c r="P22" t="s">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="Q22" t="s">
-        <v>323</v>
+        <v>342</v>
       </c>
       <c r="R22" t="s">
-        <v>346</v>
+        <v>364</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2691,34 +2745,34 @@
         <v>159</v>
       </c>
       <c r="I23" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="J23" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="K23" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="L23" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="M23" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="N23" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="O23" t="s">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="P23" t="s">
-        <v>300</v>
+        <v>319</v>
       </c>
       <c r="Q23" t="s">
-        <v>324</v>
+        <v>343</v>
       </c>
       <c r="R23" t="s">
-        <v>347</v>
+        <v>365</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2747,34 +2801,34 @@
         <v>160</v>
       </c>
       <c r="I24" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="J24" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="K24" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="L24" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="M24" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="N24" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="O24" t="s">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="P24" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
       <c r="Q24" t="s">
-        <v>325</v>
+        <v>344</v>
       </c>
       <c r="R24" t="s">
-        <v>348</v>
+        <v>366</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2806,7 +2860,7 @@
         <v>101</v>
       </c>
       <c r="J25" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="K25" t="s">
         <v>101</v>
@@ -2815,13 +2869,13 @@
         <v>101</v>
       </c>
       <c r="M25" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="N25" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="O25" t="s">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="P25" t="s">
         <v>101</v>
@@ -2859,34 +2913,34 @@
         <v>161</v>
       </c>
       <c r="I26" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="J26" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="K26" t="s">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="L26" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="M26" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="N26" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="O26" t="s">
-        <v>282</v>
+        <v>302</v>
       </c>
       <c r="P26" t="s">
-        <v>302</v>
+        <v>321</v>
       </c>
       <c r="Q26" t="s">
-        <v>326</v>
+        <v>345</v>
       </c>
       <c r="R26" t="s">
-        <v>349</v>
+        <v>367</v>
       </c>
     </row>
     <row r="27" spans="1:18">
@@ -2915,34 +2969,34 @@
         <v>162</v>
       </c>
       <c r="I27" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="J27" t="s">
         <v>101</v>
       </c>
       <c r="K27" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="L27" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="M27" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="N27" t="s">
         <v>101</v>
       </c>
       <c r="O27" t="s">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="P27" t="s">
-        <v>303</v>
+        <v>322</v>
       </c>
       <c r="Q27" t="s">
-        <v>327</v>
+        <v>346</v>
       </c>
       <c r="R27" t="s">
-        <v>350</v>
+        <v>368</v>
       </c>
     </row>
     <row r="28" spans="1:18">
@@ -2971,34 +3025,34 @@
         <v>163</v>
       </c>
       <c r="I28" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="J28" t="s">
         <v>101</v>
       </c>
       <c r="K28" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="L28" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="M28" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="N28" t="s">
         <v>101</v>
       </c>
       <c r="O28" t="s">
-        <v>284</v>
+        <v>304</v>
       </c>
       <c r="P28" t="s">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="Q28" t="s">
-        <v>328</v>
+        <v>347</v>
       </c>
       <c r="R28" t="s">
-        <v>351</v>
+        <v>369</v>
       </c>
     </row>
     <row r="29" spans="1:18">
@@ -3027,34 +3081,34 @@
         <v>164</v>
       </c>
       <c r="I29" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="J29" t="s">
         <v>101</v>
       </c>
       <c r="K29" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="L29" t="s">
         <v>101</v>
       </c>
       <c r="M29" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="N29" t="s">
         <v>101</v>
       </c>
       <c r="O29" t="s">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="P29" t="s">
-        <v>305</v>
+        <v>324</v>
       </c>
       <c r="Q29" t="s">
         <v>101</v>
       </c>
       <c r="R29" t="s">
-        <v>352</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>
